--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.67564528715261</v>
+        <v>1.7347923591623</v>
       </c>
       <c r="D2" t="n">
-        <v>10.84550297266112</v>
+        <v>1.762394233057432</v>
       </c>
       <c r="E2" t="n">
-        <v>3.786811761162589</v>
+        <v>0.6153569111889208</v>
       </c>
       <c r="F2" t="n">
-        <v>3.626154522808085</v>
+        <v>0.5892501099563139</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.98659044209662</v>
+        <v>3.247820946840701</v>
       </c>
       <c r="D3" t="n">
-        <v>19.85526925553458</v>
+        <v>3.22648125402437</v>
       </c>
       <c r="E3" t="n">
-        <v>3.786811761162589</v>
+        <v>0.6153569111889208</v>
       </c>
       <c r="F3" t="n">
-        <v>3.626154522808085</v>
+        <v>0.5892501099563139</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.1804237582574</v>
+        <v>2.954318860716828</v>
       </c>
       <c r="D4" t="n">
-        <v>17.98440089880063</v>
+        <v>2.922465146055103</v>
       </c>
       <c r="E4" t="n">
-        <v>3.786811761162589</v>
+        <v>0.6153569111889208</v>
       </c>
       <c r="F4" t="n">
-        <v>3.626154522808085</v>
+        <v>0.5892501099563139</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.89452941646822</v>
+        <v>2.095361030176085</v>
       </c>
       <c r="D5" t="n">
-        <v>13.09094275152795</v>
+        <v>2.127278197123291</v>
       </c>
       <c r="E5" t="n">
-        <v>3.786811761162589</v>
+        <v>0.6153569111889208</v>
       </c>
       <c r="F5" t="n">
-        <v>3.626154522808085</v>
+        <v>0.5892501099563139</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
